--- a/mmlu/Experiments/LLama4_17b/Experiment_mmlu.xlsx
+++ b/mmlu/Experiments/LLama4_17b/Experiment_mmlu.xlsx
@@ -518,28 +518,28 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I2" t="n">
-        <v>316</v>
+        <v>394</v>
       </c>
       <c r="J2" t="n">
-        <v>464</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>1.628e-05</v>
+        <v>1.727e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00010744</v>
+        <v>0.00013396</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00012372</v>
+        <v>0.00015123</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="3">
@@ -556,39 +556,39 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(0.0, 0.0)</t>
+          <t>(-5.853102368087347, 6.853102368087347)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="I3" t="n">
-        <v>479</v>
+        <v>688</v>
       </c>
       <c r="J3" t="n">
-        <v>923</v>
+        <v>1150</v>
       </c>
       <c r="K3" t="n">
-        <v>4.884e-05</v>
+        <v>5.081999999999999e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00016286</v>
+        <v>0.00023392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002117</v>
+        <v>0.00028474</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="4">
@@ -616,28 +616,28 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>564</v>
+        <v>768</v>
       </c>
       <c r="I4" t="n">
-        <v>404</v>
+        <v>583</v>
       </c>
       <c r="J4" t="n">
-        <v>968</v>
+        <v>1351</v>
       </c>
       <c r="K4" t="n">
-        <v>6.204e-05</v>
+        <v>8.447999999999999e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00013736</v>
+        <v>0.00019822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001994</v>
+        <v>0.0002827</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.13</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="5">
@@ -665,28 +665,28 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1486</v>
+        <v>1781</v>
       </c>
       <c r="I5" t="n">
-        <v>960</v>
+        <v>1222</v>
       </c>
       <c r="J5" t="n">
-        <v>2446</v>
+        <v>3003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00016346</v>
+        <v>0.00019591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003264</v>
+        <v>0.00041548</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004898600000000001</v>
+        <v>0.00061139</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.62</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="6">
@@ -714,28 +714,28 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="I6" t="n">
-        <v>693</v>
+        <v>843</v>
       </c>
       <c r="J6" t="n">
-        <v>989</v>
+        <v>1157</v>
       </c>
       <c r="K6" t="n">
-        <v>3.256e-05</v>
+        <v>3.454e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00023562</v>
+        <v>0.00028662</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00026818</v>
+        <v>0.00032116</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="7">
@@ -763,28 +763,28 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>888</v>
+        <v>924</v>
       </c>
       <c r="I7" t="n">
-        <v>1228</v>
+        <v>1412</v>
       </c>
       <c r="J7" t="n">
-        <v>2116</v>
+        <v>2336</v>
       </c>
       <c r="K7" t="n">
-        <v>9.768e-05</v>
+        <v>0.00010164</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00041752</v>
+        <v>0.00048008</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0005152000000000001</v>
+        <v>0.00058172</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.09</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="8">
@@ -812,28 +812,28 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1946</v>
+        <v>2522</v>
       </c>
       <c r="I8" t="n">
-        <v>1434</v>
+        <v>1649</v>
       </c>
       <c r="J8" t="n">
-        <v>3380</v>
+        <v>4171</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00021406</v>
+        <v>0.00027742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00048756</v>
+        <v>0.00056066</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00070162</v>
+        <v>0.0008380800000000001</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="9">
@@ -861,28 +861,28 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4502</v>
+        <v>5214</v>
       </c>
       <c r="I9" t="n">
-        <v>2912</v>
+        <v>3099</v>
       </c>
       <c r="J9" t="n">
-        <v>7414</v>
+        <v>8313</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00049522</v>
+        <v>0.00057354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00099008</v>
+        <v>0.00105366</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0014853</v>
+        <v>0.0016272</v>
       </c>
       <c r="N9" t="n">
         <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>8.5</v>
+        <v>6.85</v>
       </c>
     </row>
   </sheetData>
